--- a/Assets/06 Data/ExcelData/dt_player_base_stats.xlsx
+++ b/Assets/06 Data/ExcelData/dt_player_base_stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\덕코프 기획\데이터테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C89408-5EC3-4E44-8A38-7556C130A7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206E5E59-78FF-4762-94C3-BF7C48CB43E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2805" yWindow="3285" windowWidth="24300" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -234,6 +234,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -620,8 +623,8 @@
       <c r="D4" s="6">
         <v>100</v>
       </c>
-      <c r="E4" s="5">
-        <v>0.1</v>
+      <c r="E4" s="8">
+        <v>0.01</v>
       </c>
       <c r="F4" s="5">
         <v>0.1</v>

--- a/Assets/06 Data/ExcelData/dt_player_base_stats.xlsx
+++ b/Assets/06 Data/ExcelData/dt_player_base_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206E5E59-78FF-4762-94C3-BF7C48CB43E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47E084A-27B1-4474-9745-17AEE9B05A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="3285" windowWidth="24300" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
-  <si>
-    <t>uint</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>float</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -51,10 +47,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>uint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SP 회복 주기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -101,6 +93,10 @@
   <si>
     <t>HungerLossPerSec</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -534,80 +530,80 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">

--- a/Assets/06 Data/ExcelData/dt_player_base_stats.xlsx
+++ b/Assets/06 Data/ExcelData/dt_player_base_stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47E084A-27B1-4474-9745-17AEE9B05A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D3C9FB-DCC0-41A9-A3B7-54840ED4F7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -608,7 +608,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B4" s="4">
         <v>100</v>
